--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.11872943070386</v>
+        <v>1.644293532489377</v>
       </c>
       <c r="D2" t="n">
-        <v>7.508275169847407</v>
+        <v>1.220094715100204</v>
       </c>
       <c r="E2" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F2" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.01511174928866</v>
+        <v>1.789955659259407</v>
       </c>
       <c r="D3" t="n">
-        <v>10.69098624220133</v>
+        <v>1.737285264357717</v>
       </c>
       <c r="E3" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F3" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.02115552580524</v>
+        <v>2.928437772943353</v>
       </c>
       <c r="D4" t="n">
-        <v>13.58741349479764</v>
+        <v>2.207954692904617</v>
       </c>
       <c r="E4" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F4" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.11251468498335</v>
+        <v>4.243283636309794</v>
       </c>
       <c r="D5" t="n">
-        <v>15.15562788830474</v>
+        <v>2.462789531849521</v>
       </c>
       <c r="E5" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F5" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.9369750922519</v>
+        <v>5.677258452490934</v>
       </c>
       <c r="D6" t="n">
-        <v>11.06523568940275</v>
+        <v>1.798100799527946</v>
       </c>
       <c r="E6" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F6" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.71132008448078</v>
+        <v>5.965589513728127</v>
       </c>
       <c r="D7" t="n">
-        <v>26.55948661412112</v>
+        <v>4.315916574794682</v>
       </c>
       <c r="E7" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F7" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.47486496226652</v>
+        <v>4.62716555636831</v>
       </c>
       <c r="D8" t="n">
-        <v>15.07962245438796</v>
+        <v>2.450438648838043</v>
       </c>
       <c r="E8" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F8" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.87023024193613</v>
+        <v>7.453912414314621</v>
       </c>
       <c r="D9" t="n">
-        <v>16.56179027073408</v>
+        <v>2.691290918994287</v>
       </c>
       <c r="E9" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F9" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.58108344772085</v>
+        <v>6.269426060254639</v>
       </c>
       <c r="D10" t="n">
-        <v>11.52323364252617</v>
+        <v>1.872525466910503</v>
       </c>
       <c r="E10" t="n">
-        <v>11.86211256240341</v>
+        <v>1.927593291390555</v>
       </c>
       <c r="F10" t="n">
-        <v>5.104255856235377</v>
+        <v>0.8294415766382487</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
